--- a/excel/used_data/ai-post-train-new-data.xlsx
+++ b/excel/used_data/ai-post-train-new-data.xlsx
@@ -618,7 +618,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -629,6 +629,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -665,10 +671,10 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -2498,7 +2504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="19.5">
       <c r="A190" s="1" t="s">
         <v>184</v>
       </c>
@@ -2506,7 +2512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="19.5">
       <c r="A191" s="1" t="s">
         <v>185</v>
       </c>
@@ -2514,7 +2520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="19.5">
       <c r="A192" s="1" t="s">
         <v>186</v>
       </c>
@@ -2522,7 +2528,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="19.5">
       <c r="A193" s="1" t="s">
         <v>187</v>
       </c>
@@ -2530,7 +2536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="19.5">
       <c r="A194" s="1" t="s">
         <v>188</v>
       </c>
@@ -2538,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="19.5">
       <c r="A195" s="1" t="s">
         <v>189</v>
       </c>
@@ -2546,7 +2552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="19.5">
       <c r="A196" s="1" t="s">
         <v>190</v>
       </c>
@@ -2554,7 +2560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="19.5">
       <c r="A197" s="1" t="s">
         <v>191</v>
       </c>
@@ -2562,7 +2568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="19.5">
       <c r="A198" s="1" t="s">
         <v>192</v>
       </c>
@@ -2570,7 +2576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="19.5">
       <c r="A199" s="1" t="s">
         <v>193</v>
       </c>
@@ -2578,7 +2584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="19.5">
       <c r="A200" s="1" t="s">
         <v>194</v>
       </c>
@@ -2586,7 +2592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="19.5">
       <c r="A201" s="1" t="s">
         <v>195</v>
       </c>

--- a/excel/used_data/ai-post-train-new-data.xlsx
+++ b/excel/used_data/ai-post-train-new-data.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Denny\Downloads\acct-cik\excel\used_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C66B3A7-8F73-445D-AE16-741EFB8412F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="235">
   <si>
     <t>sentence</t>
   </si>
@@ -611,14 +617,121 @@
   </si>
   <si>
     <t>&lt;reportingYear&gt;2015&lt;/reportingYear&gt; We adhere to an investment policy set by our investment committee, which aims to preserve our financial assets, maintain adequate liquidity and maximize return while minimizing exposure to the NIS. Such policy further provides that we should hold most of our current assets in bank deposits and the remainder of our current assets should be invested in government bonds and a combination of corporate bonds and relatively low risk stocks. As of today, the currency of our financial portfolio is mainly in U.S. dollars and we use forward and options contracts in order to hedge our exposures to currencies other than the U.S. dollar.   Interest Rate Risk  We invest a major portion of our cash surplus in bank deposits in banks in Israel.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2012&lt;/reportingYear&gt; Synergy raised gross proceeds of $415,309 as a result of the warrant exercise. The purchase price paid by the warrant holder was $5.00 for 49,383 shares and $5.50 for 30,617 shares. Based upon the Company’s analysis of the criteria contained in ASC Topic 815-40, Synergy had determined that the warrants exercised in connection with this transaction were derivative liabilities when issued and the Company had been marking this liability to market at the end of each reporting period.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2010&lt;/reportingYear&gt; The purchase price paid by the investor was $4.05 for each unit. The warrants expire after five years and are exercisable at $4.25 per share. In accordance with ASC 815-40, "Derivatives and Hedging—Contracts in Entity's Own Equity" the warrants have been classified as a derivative liability.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2014&lt;/reportingYear&gt; Our selling, general and administrative expenses were $72.5 million during the year ended December 31, 2014 as compared to $55.6 million for the year ended December 31, 2013, an increase of $16.9 million or 30.4%. This increase was mainly due to the increase in compensation and travel due to the expansion of our sales force during the year ended December 31, 2014 and an increase in marketing expenses such as sample distribution to support the growth of Oxtellar XR and Trokendi XR. Interest Expense. Interest expense was $5.0 million during the year ended December 31, 2014 as compared to $7.8 million for the year ended December 31, 2013. The decrease of $2.8 million was primarily due to a decrease in the principal amount of our outstanding 7.5% Convertible Senior Secured Notes due in 2019 (the "Notes") from $49.5 million at January 1, 2014 to $36.1 million at December 31, 2014. Changes in Fair Value of Derivative Liability.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2015&lt;/reportingYear&gt; For the year ended December 31, 2015, we incurred a $15,095 gain on change in fair value of our derivative liabilities compared to a gain of $425,953 the same period last year. Inflation Our opinion is that inflation has not had, and is not expected to have, a material effect on our operations. Climate Change Our opinion is that neither climate change, nor governmental regulations related to climate change, have had, or are expected to have, any material effect on our operations.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2014&lt;/reportingYear&gt; These embedded derivatives included certain and anti-dilutive (reset) provisions. The accounting treatment of derivative financial instruments requires that the Company record fair value of the derivatives as of the inception date and to fair value as of each subsequent reporting date. At December 31, 2014, the fair value of the reset provision related to the embedded derivative liability of $149,920 was determined using the Binomial Option Pricing model with the following assumptions: dividend yield: 0%; volatility: 146.33%; risk free rate: 1.97%; and expected life: 7.75 years.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2013&lt;/reportingYear&gt; The estimated fair values were determined using a Monte Carlo option pricing model based on various assumptions. The Company’s derivative liabilities are adjusted to reflect estimated fair value at each period end, with any decrease or increase in the estimated fair value being recorded in other income or expense accordingly, as adjustments to fair value of derivative liabilities. On February 21, 2012, Series C Warrants to purchase an aggregate of 4,000,000 shares of the Company’s stock expired unexercised.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2022&lt;/reportingYear&gt; To determine the estimated fair value of the Change of Control Derivative Liability – Related Party, the Company used a combination of probability analysis and Monte Carlo simulation methodology. Probabilities were used to establish a distribution of time to a financing or change of control and the Monte Carlo simulation was used to forecast future equity values at the time of either event, which then were used to estimate the future values of the Convertible Notes upon conversion or payout upon either event. The key inputs to the Monte Carlo simulation included inputs including the common stock price, volatility of common stock, the risk-free interest rate and the probability of conversion into common shares at the conversion rate in the event of a change in control or major transaction (e.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2022&lt;/reportingYear&gt; In particular, management makes estimates with respect to revenue recognition, inventory valuation, the fair values of derivative liabilities, stock-based compensation expense, deferred royalty obligation, lease accounting, and income taxes. Appropriate adjustments, if any, to the estimates used are made prospectively based upon such periodic evaluation. Actual results could differ from those estimates.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2021&lt;/reportingYear&gt; The Company reviews the terms of debt instruments, equity instruments, and other financing arrangements to determine whether there are embedded derivative features, including embedded conversion options that are required to be bifurcated and accounted for separately as a derivative financial instrument. Additionally, in connection with the issuance of financing instruments, the Company may issue freestanding options and warrants, including options or warrants to non-employees in exchange for consulting or other services performed. The Company accounts for its common stock warrants in accordance with Accounting Standards Codification (“ASC”) 815, Derivatives and Hedging (“ASC 815”).</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2019&lt;/reportingYear&gt; See Note 4 and 5 for discussion regarding warrants issued with a convertible note payable. 27 NOTE 7 – STOCKHOLDERS’ DEFICIT During 2018, the Company entered into convertible loan agreements with third parties that included 505,838 5-year warrants to purchase a share of common stock at prices ranging from $0.39 to $13.20. On the date of issuance, the Company accounted for the conversion feature on the warrants as derivative liabilities, see Note 5. Derivative accounting applies as the number of warrants and the conversion prices are variable and do not have a floor as to the number of common shares in which could be converted. For the year ended December 31, 2018 the initial issuance of 505,838 warrants were increased by 2,629,883 to reflect the terms of the warrant agreement.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2022&lt;/reportingYear&gt; Critical accounting estimates Significant assumptions about the future that management has made that could result in a material adjustment to the carrying amounts of assets and liabilities, in the event that actual results differ from assumptions made, relate to, but are not limited to, the following: ● the inputs used in the Black-Scholes valuation model, including unobservable assumptions when the Corporation was private at the time of issuance of certain equity instruments (share price and volatility), in accounting for share-based payment transactions; ● the valuation of the derivative liability; ● the estimate of the percentage of completion of certain research and development agreements; ● the valuation of income tax accounts; and ● the initial valuation and estimated useful lives of intangible assets. Critical accounting judgments ● management applied judgment in determining the functional currency of the Corporation as Canadian dollars; ● management applied judgment in determining the Corporation’s ability to continue as a going concern. The Corporation has incurred significant losses since inception.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2016&lt;/reportingYear&gt; This variation was the result of the change in fair value of the derivative liabilities during the period which resulted from relative consistencies in the share price of CEL-SCI’s common stock. 50 Interest expense decreased by approximately $13,000 during the year ended September 30, 2015 compared to the year ended September 30, 2014, and consisted primarily of interest expense on the loan from CEL-SCI’s former president and interest on a capital lease. Effective July 7, 2015, the interest rate on the related party loan was reduced from 15% to 9%, resulting in approximately less interest expense during 2015 than in 2014. Additionally, the modifications of the loan from de Clara Trust were determined to be substantive, resulting in an extinguishment loss of approximately $620,000 during 2015. Research and Development Expenses During the five years ended September 30, 2016, CEL-SCI’s research and development efforts involved Multikine and LEAPS. The table below shows the research and development expenses associated with each project during this five-year period.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2017&lt;/reportingYear&gt; · Even though the shares are restricted the underlying assumption is that any restriction on resale will be removed either through registration or the passage of time at the time of issuance. The fair value of the compound embedded derivatives of the Series C Convertible Debenture at June 30, 2017 and 2016 was $32,213 and $343,673, respectively. Note 8 – Equity Transactions Fiscal Year Ended June 30, 2015 Transactions On July 17, 2014, the Company filed a registration statement on Form S-3 (the “Form S-3”) registering an aggregate of 3,071,986 shares of common stock underlying warrants previously issued by the Company in various private placement offerings between 2005 and September 2009, (“Old Warrants”) as described more fully in the Form S-3 (the “Registered Warrants”).</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2023&lt;/reportingYear&gt; As consideration for Blackstone Life Sciences’ funding for certain vutrisiran and zilebesiran clinical development costs, we have agreed to pay Blackstone Life Sciences fixed success-based payments upon achievement of specific milestones for vutrisiran and zilebesiran as well as a 1% royalty on net sales of vutrisiran for ten years. The development derivative liability is recorded at fair value and represents our current estimate of the expected future payments to Blackstone Life Sciences. The development derivative liability is based on the probability weighted present value of the estimated cash flows pursuant to contractual terms of the Funding Agreement.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2018&lt;/reportingYear&gt; , stock split); or (c) the Company issues new securities for consideration less than the exercise price. Under ASC 815, warrants that provide for down-round exercise price protection are recognized as derivative liabilities. The conversion feature within the Series F Preferred Shares was determined to not be clearly and closely related to the identified host instrument and, as such, was recognized as a derivative liability measured at fair value pursuant to ASC 815. F- 23 The initial fair value of the warrants and bifurcated embedded conversion feature, estimated to be approximately $4.3 million and $9.3 million, respectively, was deducted from the gross proceeds of the Unit offering to arrive at the initial discounted carrying value of the Series F Preferred Shares.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2018&lt;/reportingYear&gt; The fair value of the conversion feature is classified as a liability in the financial statements, with the change in fair value during the periods presented recorded in the statement of operations. F- 12 During the years ended December 31, 2018 and 2017, we recorded a gain of approximately $1.1 million and a loss of approximately $0.1 million, respectively, related to the change in fair value of the derivative liabilities during the periods. For purpose of determining the fair market value of the derivative liability, the Company used Black Scholes option valuation model.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2012&lt;/reportingYear&gt; The purchase price paid by the investors for 1,105,000 of the units sold in the fourth quarter of 2012 was $4.00 each, determined by the market price on NASDAQ. The warrants expire after five years and are exercisable at $5.32 per share. The Company paid $24,989 in cash for a finder’s fee. Based upon the Company’s analysis of the criteria contained in ASC Topic 815-40, Trovagene has determined that the warrants issued in connection with these private placements should be recorded as derivative liabilities at the time of issuance since they are all price protected (Note 5).</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2013&lt;/reportingYear&gt; The Company validates the prices developed using the market-observable data by obtaining market values from other pricing sources, analyzing pricing data in certain instances and confirming that the relevant markets are active. The Company entered into an interest rate swap agreement in September 2011 which is described in greater detail in Note 12, Derivative Instruments . The fair value of the Company's interest rate swap agreement was based on an income approach, which excludes accrued interest, and takes into consideration then-current interest rates and the then-current creditworthiness of the Company or the counterparty, as applicable.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2023&lt;/reportingYear&gt; The Company considered the carrying value of its convertible promissory note (Note 8) as of December 31, 2022 to approximate fair value due to its short-term nature. The derivative liability was recorded at its estimated fair value prior to its derecognition in March 2023 upon conversion of the associated convertible promissory notes. Fair Value Measurements The Company utilizes valuation techniques that maximize the use of observable inputs and minimize the use of unobservable inputs to the extent possible.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2020&lt;/reportingYear&gt; The development derivative liability is considered a level 3 fair value measurement, as it is dependent upon significant unobservable inputs. The derivative is valued using a scenario-based discounted cash flow method, whereby each scenario makes assumptions regarding the probability and timing of cash flows, and the present value of such cash flows is determined valued using a risk-adjusted discount rate. The fair value of the Future Warrants was estimated as of the inception of the agreement and as of December 31, 2020, using the Black Scholes Merton valuation model, with the following ranges of assumptions: volatility of 80.36% -80.76%, simulated share price of $0.11 based on a Monte Carlo model, risk-free rate of 0.17% - 0.19%, a term of 3 years and 9.6% - 10.5% discount for lack of marketability.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2015&lt;/reportingYear&gt; The $5.1 million excess of the fair value of the derivative liability over the $5.0 million of proceeds from the October 2012 Notes was recorded as other expense at the time of the closing of the transaction. Exchange Notes, 2012 Notes Additionally, in October 2012 the Company and the holders of the March 2012 Notes agreed to exchange all of the March 2012 Notes for notes with substantially similar terms as the October 2012 Notes (the “Exchange Notes” and together with the October 2012 Notes, the “2012 Notes”), except that the holders of the Exchange Notes were not entitled to receive any upfront or deferred shares of the Company’s common stock. 2013 Notes In 2013, the Company issued $4.8 million in aggregate principal amount of additional convertible promissory notes to certain investors, including existing stockholders (the “2013 Notes”).</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2014&lt;/reportingYear&gt; Level 3 – inputs that are unobservable (for example, the probability of a capital raise in a “binomial” methodology for valuation of a derivative liability directly related to the issuance of common stock warrants). The Company has entered into certain financial instruments and contracts such as, equity financing arrangements for the issuance of common stock, which include anti-dilution arrangements and detachable stock warrants that are i) not afforded equity classification, ii) embody risks not clearly and closely related to host contracts, or iii) may be net-cash settled by the counterparty. These instruments are recorded as derivative liabilities at fair value at the issuance date.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2016&lt;/reportingYear&gt; Included in SG&amp;A expenses was a break fee of $1.6 billion , which was tax deductible, paid by Abb Vie to Shire in October 2014 as a result of the termination of the proposed combination. In addition, the company recorded $666 million of net foreign exchange losses primarily due to undesignated forward contracts that were entered into to hedge anticipated foreign currency cash outflows associated with the terminated proposed combination with Shire and the exit of certain foreign currency positions. The forward contracts were settled in 2014. In the first quarter of 2015, Abb Vie recorded additional foreign exchange losses of $170 million to reflect the completed liquidation of its remaining foreign currency positions.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2014&lt;/reportingYear&gt; Debt in default is related to convertible debt issued during the year ended December 31, 2012 and prior where the convertible debt was never converted to common stock or principle repaid. The Company is in the process of contacting the remaining debt holders and negotiating settlement of the debt. Note 9: Derivative Liabilities The Company identified various derivatives in the form of freestanding warrants and conversion features embedded within convertible preferred stock issued during the years ended December 31, 2014, 2013 and 2012 as follows.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2021&lt;/reportingYear&gt; We value our interest rate swaps using observable inputs including interest rate curves, risk adjusted discount rates, credit spreads and other relevant data. Valuation of our financial commodity derivative contracts is determined using observable commodity price curves and other relevant data. We estimate the fair values of our FX derivative instruments using observable FX rates and other relevant data.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2017&lt;/reportingYear&gt; We anticipate our selling, general and administrative expenses will increase significantly as we continue to support the commercialization of GOCOVRI. Interest and other income (expense), net Interest and other income (expense), net, consists primarily of changes in fair value of the embedded derivative liability related to our Royalty-Backed Loan with HCRP, in addition to interest received on our investments. Interest expense Interest expense consists of accrued interest pursuant to our Royalty-Backed Loan and amortization of debt issuance costs. Interest expense over the life of the Royalty-Backed Loan includes an annual interest rate of 11% on the outstanding principal, a royalty rate of 6.25% on net sales of GOCOVRI after the principal amount is paid, and amortization of the debt discount.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2019&lt;/reportingYear&gt; Significant estimates during the years ended December 31, 2019 and 2018 include the valuation of liabilities of discontinued operations, useful life of property and equipment, valuation of operating lease right-of-use (“ROU”) assets and liabilities, assumptions used in assessing impairment of long-term assets, estimates of current and deferred income taxes and deferred tax valuation allowances, the fair value of non-cash equity transactions and the valuation of derivative liabilities. Concentrations Generally, the Company relies on one vendor as a single source of raw materials to produce certain components of its cancer treatment products. Any production shortfall that impairs the supply of the antigen in Prosca Vax™ to the Company could have a material adverse effect on the Company’s business, financial condition and results of operations.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2011&lt;/reportingYear&gt; If the U.S. dollar strengthens relative to the currency of the hedged anticipated sales, the increase in the fair value of the forward contracts offsets the decrease in the expected future U.S. dollar cash flows of the hedged foreign currency sales. Conversely, if the U.S. dollar weakens, the decrease in the fair value of the forward contracts offsets the increase in the value of the anticipated foreign currency cash flows. While a weaker U.S. dollar would result in a net benefit, the market value of Merck’s hedges would have declined by an estimated $330 million and $256 million, respectively, from a uniform 10% weakening of the U.S. dollar at December 31, 2011 and 2010. The market value was determined using a foreign exchange option pricing model and holding all factors except exchange rates constant.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2016&lt;/reportingYear&gt; As of December 31, 2016, we held the following derivative financial instruments, denominated in US dollars: 2016 Notional Fair Value Maturity USD forward sale contracts 42,430 (1,605 ) 2017 to 2018 USD forward purchase contracts — — Total derivative financial instruments (1,605 ) of which : Derivative financial assets — Derivative financial liabilities (1,605 ) We do not apply hedge accounting to these instruments. Liquidity risk Our financial debt consists of finance lease liabilities (€64 thousand as of December 31, 2016). We have incurred losses and cumulative negative cash flows from operations since our inception in 2000, and we anticipate that we will continue to incur losses for at least the next several years.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2023&lt;/reportingYear&gt; Foreign exchange gains and losses resulting from the settlement of such transactions and from the transaction at period end exchange rates of monetary assets and liabilities denominated in foreign currencies are recognized in net loss, except when they are deferred in equity as qualifying cash flow hedges and qualifying net investment hedges or attributable to part of the net investment in a foreign operation. Non-monetary items that are measured at fair value in a foreign currency are translated using the exchange rates at the date when the fair value was determined. Translation differences on assets and liabilities carried at fair value are reported as part of the fair value gain or loss.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2015&lt;/reportingYear&gt; We also recorded a reduction of $0.3 million in cost of goods sold related to RAVICTI as a result of an adjustment to the carrying value of the contingent royalties to reflect updated estimates of future RAVICTI sales. Fair Value of Financial Instruments The carrying amounts of our financial instruments, including cash and cash equivalents, restricted cash, accounts receivable, accounts payable and accrued expenses, approximate their fair values due to their short maturities. At December 31, 2013 and at the final measurement on June 27, 2014, the estimated fair value of our derivative liability related to the convertible portion of our Convertible Senior Notes was derived utilizing the binomial lattice approach for the valuation of convertible instruments.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2015&lt;/reportingYear&gt; On February 28, 2013, in connection with the refinancing of the Company’s €44.9 million term loan, Catalent de-designated €35.0 million of the €240.0 million notional Euribor-based interest-rate swap. Prior to de-designation, the effective portion of the change in fair value of the derivative was recorded as a component of other comprehensive income/(loss). The other comprehensive income/(loss) balance associated with the de-designated portion of the derivative was reclassified to earnings when the originally hedged forecasted interest payments on the hedged debt affected earnings.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2015&lt;/reportingYear&gt; Our revenues also are subject to foreign exchange rate fluctuations due to the global nature of our operations. Although we have foreign currency forward contracts to hedge forecasted product revenues denominated in foreign currencies, our efforts to reduce currency exchange losses may not be successful. As a result, currency fluctuations among our reporting currency, the U.S. dollar, and the currencies in which we do business may affect our operating results, often in unpredictable ways.</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2015&lt;/reportingYear&gt; During the three months ended September 28, 2013, we entered into forward interest rate swap agreements to hedge against changes in the benchmark interest rate between the date the swap agreements were entered into and the date of the issuance of our 2013 Bonds, discussed in Note 10 . These swaps were designated as cash flow hedges of expected future debt issuances with a notional amount totaling $725.0 million . The interest rate swaps were settled upon the issuance of an aggregate $2.3 billion principal amount of our 2013 Bonds on December 18, 2013 for a cumulative after-tax loss of $12.8 million in OCI after recording $0.5 million of ineffectiveness to Other expense, net, during the fiscal year ended June 28, 2014 .</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>&lt;reportingYear&gt;2018&lt;/reportingYear&gt; F-30 Contractual maturities of debt obligations The aggregate contractual maturities of all borrowings due subsequent to December 31, 2018 , are as follows (in millions): Maturity dates Amounts 2019 $ 4,424 2020 2,950 2021 3,500 2022 4,183 2023 1,463 Thereafter 18,358 Total $ 34,878 Interest costs Interest costs are expensed as incurred except to the extent such interest is related to construction in progress, in which case interest is capitalized. Interest costs capitalized for the years ended December 31, 2018 , 2017 and 2016 , were not material. Interest paid, including the ongoing impact of interest rate and cross-currency swap contracts, during the years ended December 31, 2018 , 2017 and 2016 , was $1.5 billion , $1.3 billion and $1.2 billion , respectively.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -638,6 +751,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -647,7 +766,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -662,36 +781,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -702,10 +836,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -743,71 +877,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -835,7 +969,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -858,11 +992,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -871,13 +1005,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -887,7 +1021,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -896,7 +1030,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -905,7 +1039,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -913,10 +1047,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -981,1647 +1115,1927 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B204"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B239"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="1" t="s">
+      <c r="B5" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1" t="s">
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="1" t="s">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="1" t="s">
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="1" t="s">
+      <c r="B10" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="1" t="s">
+      <c r="B11" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="1" t="s">
+      <c r="B12" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="1" t="s">
+      <c r="B13" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="1" t="s">
+      <c r="B14" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="1" t="s">
+      <c r="B15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="1" t="s">
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="1" t="s">
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="1" t="s">
+      <c r="B18" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="1" t="s">
+      <c r="B20" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="1" t="s">
+      <c r="B21" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="1" t="s">
+      <c r="B22" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="1" t="s">
+      <c r="B23" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="1" t="s">
+      <c r="B24" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="1" t="s">
+      <c r="B25" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="1" t="s">
+      <c r="B26" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="1" t="s">
+      <c r="B27" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="1" t="s">
+      <c r="B28" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="1" t="s">
+      <c r="B30" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="1" t="s">
+      <c r="B31" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="1" t="s">
+      <c r="B32" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="1" t="s">
+      <c r="B33" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="1" t="s">
+      <c r="B34" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="1" t="s">
+      <c r="B35" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="1" t="s">
+      <c r="B36" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="1" t="s">
+      <c r="B37" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="1" t="s">
+      <c r="B38" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="1" t="s">
+      <c r="B39" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="1" t="s">
+      <c r="B41" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="1" t="s">
+      <c r="B43" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="1" t="s">
+      <c r="B45" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="1" t="s">
+      <c r="B46" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="1" t="s">
+      <c r="B47" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="1" t="s">
+      <c r="B48" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="1" t="s">
+      <c r="B49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="1" t="s">
+      <c r="B50" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="1" t="s">
+      <c r="B51" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>46</v>
       </c>
-      <c r="B52" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="1" t="s">
+      <c r="B52" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="1" t="s">
+      <c r="B53" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="1" t="s">
+      <c r="B54" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="1" t="s">
+      <c r="B55" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>50</v>
       </c>
-      <c r="B56" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="1" t="s">
+      <c r="B56" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>51</v>
       </c>
-      <c r="B57" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="1" t="s">
+      <c r="B57" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>52</v>
       </c>
-      <c r="B58" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="1" t="s">
+      <c r="B58" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>53</v>
       </c>
-      <c r="B59" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="1" t="s">
+      <c r="B59" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>54</v>
       </c>
-      <c r="B60" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="1" t="s">
+      <c r="B60" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>55</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>57</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="1" t="s">
+    <row r="64" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>58</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="1" t="s">
+    <row r="65" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>59</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="1" t="s">
+    <row r="66" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>60</v>
       </c>
-      <c r="B66" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="1" t="s">
+      <c r="B66" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>61</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="1" t="s">
+    <row r="68" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>62</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="1" t="s">
+    <row r="69" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>63</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="1" t="s">
+    <row r="70" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>64</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="1" t="s">
+    <row r="71" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>65</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="1" t="s">
+    <row r="72" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>66</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="1" t="s">
+    <row r="73" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="1" t="s">
+    <row r="74" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="1" t="s">
+    <row r="75" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="1" t="s">
+    <row r="76" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>70</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="1" t="s">
+    <row r="77" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>71</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="1" t="s">
+    <row r="78" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="1" t="s">
+    <row r="79" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>73</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="1" t="s">
+    <row r="80" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>74</v>
       </c>
-      <c r="B80" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="1" t="s">
+      <c r="B80" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>75</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="1" t="s">
+    <row r="82" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>76</v>
       </c>
-      <c r="B82" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="1" t="s">
+      <c r="B82" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>77</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
-      <c r="A84" s="1" t="s">
+    <row r="84" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>78</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
-      <c r="A85" s="1" t="s">
+    <row r="85" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>79</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
-      <c r="A86" s="1" t="s">
+    <row r="86" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>80</v>
       </c>
-      <c r="B86" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
-      <c r="A87" s="1" t="s">
+      <c r="B86" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>81</v>
       </c>
-      <c r="B87" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
-      <c r="A88" s="1" t="s">
+      <c r="B87" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>82</v>
       </c>
-      <c r="B88" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
-      <c r="A89" s="1" t="s">
+      <c r="B88" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
-      <c r="A90" s="1" t="s">
+    <row r="90" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>84</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="1" t="s">
+    <row r="91" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>85</v>
       </c>
-      <c r="B91" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
-      <c r="A92" s="1" t="s">
+      <c r="B91" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>86</v>
       </c>
-      <c r="B92" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
-      <c r="A93" s="1" t="s">
+      <c r="B92" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>87</v>
       </c>
-      <c r="B93" s="3">
+      <c r="B93" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="1" t="s">
+    <row r="94" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>88</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
-      <c r="A95" s="1" t="s">
+    <row r="95" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>89</v>
       </c>
-      <c r="B95" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="1" t="s">
+      <c r="B95" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>90</v>
       </c>
-      <c r="B96" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
-      <c r="A97" s="1" t="s">
+      <c r="B96" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>91</v>
       </c>
-      <c r="B97" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
-      <c r="A98" s="1" t="s">
+      <c r="B97" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>92</v>
       </c>
-      <c r="B98" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
-      <c r="A99" s="1" t="s">
+      <c r="B98" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>93</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
-      <c r="A100" s="1" t="s">
+    <row r="100" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>94</v>
       </c>
-      <c r="B100" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
-      <c r="A101" s="1" t="s">
+      <c r="B100" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>95</v>
       </c>
-      <c r="B101" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
-      <c r="A102" s="1" t="s">
+      <c r="B101" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>96</v>
       </c>
-      <c r="B102" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
-      <c r="A103" s="1" t="s">
+      <c r="B102" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>97</v>
       </c>
-      <c r="B103" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
-      <c r="A104" s="1" t="s">
+      <c r="B103" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>98</v>
       </c>
-      <c r="B104" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
-      <c r="A105" s="1" t="s">
+      <c r="B104" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>99</v>
       </c>
-      <c r="B105" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
-      <c r="A106" s="1" t="s">
+      <c r="B105" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>100</v>
       </c>
-      <c r="B106" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
-      <c r="A107" s="1" t="s">
+      <c r="B106" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>101</v>
       </c>
-      <c r="B107" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
-      <c r="A108" s="1" t="s">
+      <c r="B107" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>102</v>
       </c>
-      <c r="B108" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
-      <c r="A109" s="1" t="s">
+      <c r="B108" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>103</v>
       </c>
-      <c r="B109" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
-      <c r="A110" s="1" t="s">
+      <c r="B109" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>104</v>
       </c>
-      <c r="B110" s="3">
+      <c r="B110" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
-      <c r="A111" s="1" t="s">
+    <row r="111" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>105</v>
       </c>
-      <c r="B111" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
-      <c r="A112" s="1" t="s">
+      <c r="B111" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>106</v>
       </c>
-      <c r="B112" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
-      <c r="A113" s="1" t="s">
+      <c r="B112" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>107</v>
       </c>
-      <c r="B113" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
-      <c r="A114" s="1" t="s">
+      <c r="B113" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>108</v>
       </c>
-      <c r="B114" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
-      <c r="A115" s="1" t="s">
+      <c r="B114" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>109</v>
       </c>
-      <c r="B115" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
-      <c r="A116" s="1" t="s">
+      <c r="B115" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>110</v>
       </c>
-      <c r="B116" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
-      <c r="A117" s="1" t="s">
+      <c r="B116" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>111</v>
       </c>
-      <c r="B117" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
-      <c r="A118" s="1" t="s">
+      <c r="B117" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>112</v>
       </c>
-      <c r="B118" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
-      <c r="A119" s="1" t="s">
+      <c r="B118" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>113</v>
       </c>
-      <c r="B119" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
-      <c r="A120" s="1" t="s">
+      <c r="B119" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>114</v>
       </c>
-      <c r="B120" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
-      <c r="A121" s="1" t="s">
+      <c r="B120" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>115</v>
       </c>
-      <c r="B121" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
-      <c r="A122" s="1" t="s">
+      <c r="B121" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>116</v>
       </c>
-      <c r="B122" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
-      <c r="A123" s="1" t="s">
+      <c r="B122" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>117</v>
       </c>
-      <c r="B123" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
-      <c r="A124" s="1" t="s">
+      <c r="B123" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>118</v>
       </c>
-      <c r="B124" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
-      <c r="A125" s="1" t="s">
+      <c r="B124" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>119</v>
       </c>
-      <c r="B125" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
-      <c r="A126" s="1" t="s">
+      <c r="B125" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>120</v>
       </c>
-      <c r="B126" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
-      <c r="A127" s="1" t="s">
+      <c r="B126" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>121</v>
       </c>
-      <c r="B127" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
-      <c r="A128" s="1" t="s">
+      <c r="B127" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>122</v>
       </c>
-      <c r="B128" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
-      <c r="A129" s="1" t="s">
+      <c r="B128" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>123</v>
       </c>
-      <c r="B129" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
-      <c r="A130" s="1" t="s">
+      <c r="B129" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>124</v>
       </c>
-      <c r="B130" s="3">
+      <c r="B130" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
-      <c r="A131" s="1" t="s">
+    <row r="131" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
-      <c r="A132" s="1" t="s">
+      <c r="B131" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>126</v>
       </c>
-      <c r="B132" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
-      <c r="A133" s="1" t="s">
+      <c r="B132" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>127</v>
       </c>
-      <c r="B133" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
-      <c r="A134" s="1" t="s">
+      <c r="B133" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>128</v>
       </c>
-      <c r="B134" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
-      <c r="A135" s="1" t="s">
+      <c r="B134" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>129</v>
       </c>
-      <c r="B135" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
-      <c r="A136" s="1" t="s">
+      <c r="B135" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>130</v>
       </c>
-      <c r="B136" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
-      <c r="A137" s="1" t="s">
+      <c r="B136" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>131</v>
       </c>
-      <c r="B137" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
-      <c r="A138" s="1" t="s">
+      <c r="B137" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>132</v>
       </c>
-      <c r="B138" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
-      <c r="A139" s="1" t="s">
+      <c r="B138" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
         <v>133</v>
       </c>
-      <c r="B139" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
-      <c r="A140" s="1" t="s">
+      <c r="B139" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>134</v>
       </c>
-      <c r="B140" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
-      <c r="A141" s="1" t="s">
+      <c r="B140" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>135</v>
       </c>
-      <c r="B141" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
-      <c r="A142" s="1" t="s">
+      <c r="B141" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
         <v>136</v>
       </c>
-      <c r="B142" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
-      <c r="A143" s="1" t="s">
+      <c r="B142" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>137</v>
       </c>
-      <c r="B143" s="3">
+      <c r="B143" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
-      <c r="A144" s="1" t="s">
+    <row r="144" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
         <v>138</v>
       </c>
-      <c r="B144" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
-      <c r="A145" s="1" t="s">
+      <c r="B144" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>139</v>
       </c>
-      <c r="B145" s="3">
+      <c r="B145" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
-      <c r="A146" s="1" t="s">
+    <row r="146" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
         <v>140</v>
       </c>
-      <c r="B146" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
-      <c r="A147" s="1" t="s">
+      <c r="B146" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
         <v>141</v>
       </c>
-      <c r="B147" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
-      <c r="A148" s="1" t="s">
+      <c r="B147" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
         <v>142</v>
       </c>
-      <c r="B148" s="3">
+      <c r="B148" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
-      <c r="A149" s="1" t="s">
+    <row r="149" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
         <v>143</v>
       </c>
-      <c r="B149" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
-      <c r="A150" s="1" t="s">
+      <c r="B149" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>144</v>
       </c>
-      <c r="B150" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
-      <c r="A151" s="1" t="s">
+      <c r="B150" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
         <v>145</v>
       </c>
-      <c r="B151" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
-      <c r="A152" s="1" t="s">
+      <c r="B151" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
         <v>146</v>
       </c>
-      <c r="B152" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
-      <c r="A153" s="1" t="s">
+      <c r="B152" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
         <v>147</v>
       </c>
-      <c r="B153" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
-      <c r="A154" s="1" t="s">
+      <c r="B153" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>148</v>
       </c>
-      <c r="B154" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
-      <c r="A155" s="1" t="s">
+      <c r="B154" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
         <v>149</v>
       </c>
-      <c r="B155" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
-      <c r="A156" s="1" t="s">
+      <c r="B155" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>150</v>
       </c>
-      <c r="B156" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
-      <c r="A157" s="1" t="s">
+      <c r="B156" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>151</v>
       </c>
-      <c r="B157" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
-      <c r="A158" s="1" t="s">
+      <c r="B157" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>152</v>
       </c>
-      <c r="B158" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
-      <c r="A159" s="1" t="s">
+      <c r="B158" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>153</v>
       </c>
-      <c r="B159" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
-      <c r="A160" s="1" t="s">
+      <c r="B159" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>154</v>
       </c>
-      <c r="B160" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
-      <c r="A161" s="1" t="s">
+      <c r="B160" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>155</v>
       </c>
-      <c r="B161" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
-      <c r="A162" s="1" t="s">
+      <c r="B161" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>156</v>
       </c>
-      <c r="B162" s="3">
+      <c r="B162" s="2">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
-      <c r="A163" s="1" t="s">
+    <row r="163" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>157</v>
       </c>
-      <c r="B163" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
-      <c r="A164" s="1" t="s">
+      <c r="B163" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>158</v>
       </c>
-      <c r="B164" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
-      <c r="A165" s="1" t="s">
+      <c r="B164" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
         <v>159</v>
       </c>
-      <c r="B165" s="3">
+      <c r="B165" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
-      <c r="A166" s="1" t="s">
+    <row r="166" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
         <v>160</v>
       </c>
-      <c r="B166" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
-      <c r="A167" s="1" t="s">
+      <c r="B166" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
         <v>161</v>
       </c>
-      <c r="B167" s="3">
+      <c r="B167" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
-      <c r="A168" s="1" t="s">
+    <row r="168" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>162</v>
       </c>
-      <c r="B168" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
-      <c r="A169" s="1" t="s">
+      <c r="B168" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
         <v>163</v>
       </c>
-      <c r="B169" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
-      <c r="A170" s="1" t="s">
+      <c r="B169" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
         <v>164</v>
       </c>
-      <c r="B170" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
-      <c r="A171" s="1" t="s">
+      <c r="B170" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
         <v>165</v>
       </c>
-      <c r="B171" s="3">
+      <c r="B171" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
-      <c r="A172" s="1" t="s">
+    <row r="172" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>166</v>
       </c>
-      <c r="B172" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
-      <c r="A173" s="1" t="s">
+      <c r="B172" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
         <v>167</v>
       </c>
-      <c r="B173" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
-      <c r="A174" s="1" t="s">
+      <c r="B173" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
         <v>168</v>
       </c>
-      <c r="B174" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
-      <c r="A175" s="1" t="s">
+      <c r="B174" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
         <v>169</v>
       </c>
-      <c r="B175" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
-      <c r="A176" s="1" t="s">
+      <c r="B175" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
         <v>170</v>
       </c>
-      <c r="B176" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
-      <c r="A177" s="1" t="s">
+      <c r="B176" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
         <v>171</v>
       </c>
-      <c r="B177" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
-      <c r="A178" s="1" t="s">
+      <c r="B177" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
         <v>172</v>
       </c>
-      <c r="B178" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
-      <c r="A179" s="1" t="s">
+      <c r="B178" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
         <v>173</v>
       </c>
-      <c r="B179" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
-      <c r="A180" s="1" t="s">
+      <c r="B179" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
         <v>174</v>
       </c>
-      <c r="B180" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75">
-      <c r="A181" s="1" t="s">
+      <c r="B180" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
         <v>175</v>
       </c>
-      <c r="B181" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
-      <c r="A182" s="1" t="s">
+      <c r="B181" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
         <v>176</v>
       </c>
-      <c r="B182" s="3">
+      <c r="B182" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
-      <c r="A183" s="1" t="s">
+    <row r="183" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
         <v>177</v>
       </c>
-      <c r="B183" s="3">
+      <c r="B183" s="2">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75">
-      <c r="A184" s="1" t="s">
+    <row r="184" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
         <v>178</v>
       </c>
-      <c r="B184" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
-      <c r="A185" s="1" t="s">
+      <c r="B184" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
         <v>179</v>
       </c>
-      <c r="B185" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75">
-      <c r="A186" s="1" t="s">
+      <c r="B185" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
         <v>180</v>
       </c>
-      <c r="B186" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
-      <c r="A187" s="1" t="s">
+      <c r="B186" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
         <v>181</v>
       </c>
-      <c r="B187" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75">
-      <c r="A188" s="1" t="s">
+      <c r="B187" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
         <v>182</v>
       </c>
-      <c r="B188" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
-      <c r="A189" s="1" t="s">
+      <c r="B188" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
         <v>183</v>
       </c>
-      <c r="B189" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="19.5">
-      <c r="A190" s="1" t="s">
+      <c r="B189" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
         <v>184</v>
       </c>
-      <c r="B190" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="19.5">
-      <c r="A191" s="1" t="s">
+      <c r="B190" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
         <v>185</v>
       </c>
-      <c r="B191" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="19.5">
-      <c r="A192" s="1" t="s">
+      <c r="B191" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
         <v>186</v>
       </c>
-      <c r="B192" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="19.5">
-      <c r="A193" s="1" t="s">
+      <c r="B192" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
         <v>187</v>
       </c>
-      <c r="B193" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="19.5">
-      <c r="A194" s="1" t="s">
+      <c r="B193" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
         <v>188</v>
       </c>
-      <c r="B194" s="3">
+      <c r="B194" s="2">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="19.5">
-      <c r="A195" s="1" t="s">
+    <row r="195" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
         <v>189</v>
       </c>
-      <c r="B195" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="19.5">
-      <c r="A196" s="1" t="s">
+      <c r="B195" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
         <v>190</v>
       </c>
-      <c r="B196" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="19.5">
-      <c r="A197" s="1" t="s">
+      <c r="B196" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
         <v>191</v>
       </c>
-      <c r="B197" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="19.5">
-      <c r="A198" s="1" t="s">
+      <c r="B197" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
         <v>192</v>
       </c>
-      <c r="B198" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="19.5">
-      <c r="A199" s="1" t="s">
+      <c r="B198" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
         <v>193</v>
       </c>
-      <c r="B199" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="19.5">
-      <c r="A200" s="1" t="s">
+      <c r="B199" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
         <v>194</v>
       </c>
-      <c r="B200" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="19.5">
-      <c r="A201" s="1" t="s">
+      <c r="B200" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
         <v>195</v>
       </c>
-      <c r="B201" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75">
-      <c r="A202" s="1" t="s">
+      <c r="B201" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
         <v>196</v>
       </c>
-      <c r="B202" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75">
-      <c r="A203" s="1" t="s">
+      <c r="B202" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
         <v>197</v>
       </c>
-      <c r="B203" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75">
-      <c r="A204" s="1" t="s">
+      <c r="B203" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
         <v>198</v>
       </c>
-      <c r="B204" s="3">
+      <c r="B204" s="2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>232</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>231</v>
+      </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>230</v>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>229</v>
+      </c>
+      <c r="B209">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>228</v>
+      </c>
+      <c r="B210">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>227</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>226</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>225</v>
+      </c>
+      <c r="B213">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>224</v>
+      </c>
+      <c r="B214">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>223</v>
+      </c>
+      <c r="B215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>222</v>
+      </c>
+      <c r="B216">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>221</v>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>220</v>
+      </c>
+      <c r="B218">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>217</v>
+      </c>
+      <c r="B221">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>216</v>
+      </c>
+      <c r="B222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>215</v>
+      </c>
+      <c r="B223">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>214</v>
+      </c>
+      <c r="B224">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>213</v>
+      </c>
+      <c r="B225">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>212</v>
+      </c>
+      <c r="B226">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>211</v>
+      </c>
+      <c r="B227">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>210</v>
+      </c>
+      <c r="B228">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>209</v>
+      </c>
+      <c r="B229">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>208</v>
+      </c>
+      <c r="B230">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>207</v>
+      </c>
+      <c r="B231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>206</v>
+      </c>
+      <c r="B232">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>205</v>
+      </c>
+      <c r="B233">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>204</v>
+      </c>
+      <c r="B234">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>203</v>
+      </c>
+      <c r="B235">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>202</v>
+      </c>
+      <c r="B236">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>201</v>
+      </c>
+      <c r="B237">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>200</v>
+      </c>
+      <c r="B238">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>199</v>
+      </c>
+      <c r="B239">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
